--- a/data_hei/test-batch/results.xlsx
+++ b/data_hei/test-batch/results.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -845,10 +845,26 @@
           <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Kamil Jaszczuk</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Erasmus+ Program Coordinator</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kjaszczuk@panschelm.edu.pl</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rektorat@panschelm.edu.pl</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>82 562 06 13</t>
@@ -856,23 +872,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/</t>
+          <t>https://panschelm.edu.pl/erasmus/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>university</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -882,7 +898,7 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr">
@@ -948,15 +964,31 @@
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>82 562 06 13</t>
+        </is>
+      </c>
+      <c r="AD3" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/erasmus/</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>mgr Kamil Jaszczuk</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>no contact found</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+          <t>name, email, phone found on page</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Matches the contact your operators already spoke to. Mobility coordinator. Kamil Jaszczuk is explicitly listed as the contact for the Erasmus+ program at the institution with a direct phone number and email address.</t>
+        </is>
+      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>country</t>
@@ -964,7 +996,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -974,7 +1006,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>27 of 27 verified</t>
+          <t>50 of 50 verified</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -986,17 +1018,17 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>The evidence provides a specific list of Erasmus partner universities and local cooperating companies and institutions, alongside general institutional details.</t>
+          <t>The evidence provides an explicit list of partner universities and collaborating industrial partners, along with general administrative contacts.</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>site found via: website column in the sheet. mode: gemini.</t>
+          <t>site found via: remembered from an earlier run. mode: gemini.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1127,7 +1159,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>name found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1321,7 +1353,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1515,7 +1547,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1579,31 +1611,33 @@
     <hyperlink ref="N2" location="'r001 Haute Ecole Robert Schuman'!A1" display="3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId3"/>
+    <hyperlink ref="B3" location="'Contacts'!A3" display="Kamil Jaszczuk"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
-    <hyperlink ref="M3" location="'r002 Państwowa Akademia Nauk St'!A1" display="14"/>
+    <hyperlink ref="M3" location="'r002 Państwowa Akademia Nauk St'!A1" display="50"/>
     <hyperlink ref="N3" location="'r002 Państwowa Akademia Nauk St'!A1" display="2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y3" r:id="rId6"/>
-    <hyperlink ref="B4" location="'Contacts'!A3" display="Mag.a Lissa Gartler"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD3" r:id="rId7"/>
+    <hyperlink ref="B4" location="'Contacts'!A6" display="Mag.a Lissa Gartler"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId8"/>
     <hyperlink ref="M4" location="'r003 UNIVERSITAT FUR MUSIK UND'!A1" display="2"/>
     <hyperlink ref="N4" location="'r003 UNIVERSITAT FUR MUSIK UND'!A1" display="2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="rId9"/>
-    <hyperlink ref="B5" location="'Contacts'!A4" display="Tim Kaiser"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="rId10"/>
+    <hyperlink ref="B5" location="'Contacts'!A7" display="Tim Kaiser"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId11"/>
     <hyperlink ref="M5" location="'r004 PAEDAGOGISCHE HOCHSCHULE W'!A1" display="9"/>
     <hyperlink ref="N5" location="'r004 PAEDAGOGISCHE HOCHSCHULE W'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId13"/>
-    <hyperlink ref="B6" location="'Contacts'!A7" display="Ketil Akerø"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId14"/>
+    <hyperlink ref="B6" location="'Contacts'!A10" display="Ketil Akerø"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId15"/>
     <hyperlink ref="M6" location="'r005 KUNSTHOGSKOLEN I OSLO KHIO'!A1" display="14"/>
     <hyperlink ref="N6" location="'r005 KUNSTHOGSKOLEN I OSLO KHIO'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Y6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD6" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2305,7 +2339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2433,7 +2467,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -2500,7 +2534,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2567,7 +2601,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2634,7 +2668,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2701,7 +2735,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2768,7 +2802,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2835,7 +2869,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2902,7 +2936,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2969,7 +3003,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -3036,7 +3070,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -3103,7 +3137,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -3170,7 +3204,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -3237,7 +3271,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -3304,7 +3338,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -3371,7 +3405,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3438,7 +3472,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -3505,7 +3539,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3572,7 +3606,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3639,7 +3673,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3706,7 +3740,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3773,7 +3807,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3840,7 +3874,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3907,7 +3941,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3974,7 +4008,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -4041,7 +4075,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -4108,7 +4142,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4175,7 +4209,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4242,7 +4276,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4309,7 +4343,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4376,7 +4410,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4443,7 +4477,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4510,7 +4544,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4577,7 +4611,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4644,7 +4678,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4711,7 +4745,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4778,7 +4812,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4845,7 +4879,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4912,7 +4946,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4979,7 +5013,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5046,7 +5080,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5113,7 +5147,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5180,7 +5214,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5247,7 +5281,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5314,7 +5348,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5381,7 +5415,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5448,7 +5482,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5515,7 +5549,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5582,7 +5616,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5649,7 +5683,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5716,7 +5750,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5783,7 +5817,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5850,7 +5884,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5917,7 +5951,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5984,7 +6018,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6051,7 +6085,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6118,7 +6152,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6185,7 +6219,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6252,7 +6286,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6319,7 +6353,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6386,7 +6420,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6453,7 +6487,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6520,7 +6554,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6587,7 +6621,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6654,7 +6688,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6721,7 +6755,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6788,7 +6822,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6855,7 +6889,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6922,7 +6956,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6989,7 +7023,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7056,7 +7090,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7123,7 +7157,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7190,7 +7224,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7257,7 +7291,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7324,7 +7358,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7391,7 +7425,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7458,7 +7492,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -7525,7 +7559,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7592,7 +7626,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7659,7 +7693,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7726,7 +7760,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7793,7 +7827,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7860,7 +7894,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7927,7 +7961,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7994,7 +8028,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8061,7 +8095,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -8128,7 +8162,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -8195,7 +8229,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -8267,7 +8301,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8368,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8390,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8401,7 +8435,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8502,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8569,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8636,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8703,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8770,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8837,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8825,7 +8859,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8870,7 +8904,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -8937,14 +8971,14 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Instytut Ochrony Roślin – PIB</t>
+          <t>Elektrolis</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8959,7 +8993,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8989,12 +9023,12 @@
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>[Nowa współpraca PANS w Chełmie z Instytutem Ochrony Roślin – PIB]</t>
+          <t>Firma Elektrolis – szuka pracownika</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -9004,14 +9038,14 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Enter Air Training Center</t>
+          <t>Finder Polska</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9056,12 +9090,12 @@
       </c>
       <c r="J101" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Studenci PANS w Chełmie z wizytą w Enter Air Training Center w Warszawie</t>
+          <t>Podpisanie listu intencyjnego z firmą Finder Polska – nowy etap współpracy</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9071,19 +9105,19 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Erasmus Student Network (ESN)</t>
+          <t>Zespół Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9093,7 +9127,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9123,12 +9157,12 @@
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/erasmus/mobilnosc-studentow/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>W poszukiwaniu ofert można skorzystać między innymi z portalu ErasmusIntern.org, prowadzonego przez Erasmus Student Network (ESN).</t>
+          <t>Warsztaty Zespół Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -9138,24 +9172,24 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zagreber Philharmonie</t>
+          <t>ISPCH</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9180,22 +9214,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>https://www.kug.ac.at/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Festanstellung für Fran Povijač als tiefer Hornist bei der Zagreber Philharmonie</t>
+          <t>Podpisanie porozumienia o współpracy z firmą ISPCH</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9205,24 +9239,24 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-10-20T16:00:02Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Tonhalle Orchester Zürich</t>
+          <t>Zakład Produkcyjny GUMET</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9247,22 +9281,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J104" s="1" t="inlineStr">
         <is>
-          <t>https://www.kug.ac.at/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Engagement beim Tonhalle Orchester Zürich für Hornist Daniel Dubrovsky.</t>
+          <t>Wizyta przedstawicieli Zakładu Produkcyjnego GUMET z Kraśnika</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -9272,19 +9306,19 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-10-20T16:00:02Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Florida International University</t>
+          <t>Zakład Wyrobów Betonowych Wojciech Trykacz</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9294,7 +9328,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9314,22 +9348,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J105" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
+          <t>Współpraca z Zakładem Wyrobów Betonowych Wojciech Trykacz</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -9339,19 +9373,19 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Møller Institute, Churchill College, University of Cambridge</t>
+          <t>Recykl S.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9361,7 +9395,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9381,22 +9415,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J106" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
+          <t>Praca w laboratorium Recykl S.A.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -9406,19 +9440,19 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Universität Graz</t>
+          <t>PROSOLUTIONS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Österreich</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -9428,7 +9462,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9448,22 +9482,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J107" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+          <t>Rozwijamy współpracę z PROSOLUTIONS</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9473,19 +9507,19 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Universität Minho</t>
+          <t>Agro Antoniko Plus Sp. z o.o.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9495,7 +9529,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9515,22 +9549,22 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J108" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+          <t>Współpraca ze Spółką Agro Antoniko Plus Sp. z o.o.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9540,19 +9574,19 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Universität Växjö</t>
+          <t>Recykl O. O. S.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Schweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9562,7 +9596,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9582,22 +9616,22 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J109" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+          <t>Rozwijamy współpracę z Recykl O. O. S.A.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9607,19 +9641,19 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Universidade Federal de Santa Catarina</t>
+          <t>Gumet</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Brasilien</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9629,7 +9663,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9649,22 +9683,22 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J110" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Donnerstag, 22.10.26 Präsentation von Dr. Elaine Roschel, Universidade Federal de Santa Catarina, Brasilien</t>
+          <t>[Gumet]</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -9674,19 +9708,19 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Stranmillis</t>
+          <t>ZS 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nordirland</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9696,7 +9730,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9716,22 +9750,22 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J111" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Dienstag, 17.11.26 South Africa / Stranmillis (Nordirland)</t>
+          <t>[ZS 3 w Kraśniku]</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9741,19 +9775,19 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>UTALCA</t>
+          <t>Recykl Organizacja Odzysku S.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9763,7 +9797,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9783,22 +9817,22 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J112" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Dienstag, 01.12.26 Chile - Concepcion / UTALCA</t>
+          <t>[Recykl Organizacja Odzysku S.A.]</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9808,29 +9842,29 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>more than 65 partner universities</t>
+          <t>Fabryka Łożysk Tocznych w Kraśniku</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9850,22 +9884,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J113" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Darüber hinaus organisiert das International Office Austausch- und Mobilitätsprogramme mit mehr als 65 Partnerhochschulen</t>
+          <t>[Fabryka Łożysk Tocznych w Kraśniku]</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9875,19 +9909,19 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-10-20T15:58:36Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ELIA</t>
+          <t>Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9897,7 +9931,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9917,22 +9951,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J114" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/intranet/for-staff/internationalization/other-networks-and-bilateral-agreements</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>KHiO are partners in ELIA and Society for Artistic Research. We have several bilaterale agreements with partners outside of Europe.</t>
+          <t>[Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego]</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9942,19 +9976,19 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Society for Artistic Research</t>
+          <t>Muzeum Ziemi Chełmskiej im. Wiktora Ambroziewicza w Chełmie</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9964,7 +9998,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9984,22 +10018,22 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J115" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/intranet/for-staff/internationalization/other-networks-and-bilateral-agreements</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>KHiO are partners in ELIA and Society for Artistic Research. We have several bilaterale agreements with partners outside of Europe.</t>
+          <t>[Muzeum Ziemi Chełmskiej im. Wiktora Ambroziewicza w Chełmie]</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10009,19 +10043,19 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Conservatorio di Musica Santa Cecilia</t>
+          <t>Centrum Medyczne Aurismed</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -10031,7 +10065,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10051,22 +10085,22 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J116" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>The project is coordinated by Conservatorio di Musica Santa Cecilia (Rome) and the following project partners:</t>
+          <t>[Centrum Medyczne Aurismed]</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10076,19 +10110,19 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Mozarteum University Salzburg</t>
+          <t>Muzeum Regionalne w Krasnymstawie</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -10098,7 +10132,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10118,22 +10152,22 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J117" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Mozarteum University Salzburg (Austria)</t>
+          <t>[Muzeum Regionalne w Krasnymstawie]</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10143,19 +10177,19 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Stockholm University of the Arts – SKH</t>
+          <t>Haber</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10165,7 +10199,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10185,22 +10219,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J118" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Stockholm University of the Arts – SKH (Sweden)</t>
+          <t>[Haber]</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10210,19 +10244,19 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Escola Superior de Música e Artes do Espetáculo do Porto</t>
+          <t>Sigma</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10232,7 +10266,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10252,22 +10286,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J119" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Escola Superior de Música e Artes do Espetáculo do Porto (Portugal)</t>
+          <t>[Sigma]</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10277,19 +10311,19 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nova Opera</t>
+          <t>Erasmus Student Network (ESN)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -10299,7 +10333,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>network</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10319,22 +10353,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J120" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/erasmus/mobilnosc-studentow/</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Nova Opera (Ukraine)</t>
+          <t>W poszukiwaniu ofert można skorzystać między innymi z portalu ErasmusIntern.org, prowadzonego przez Erasmus Student Network (ESN).</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -10344,19 +10378,19 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WallMuse</t>
+          <t>Uczelniana Rada Samorządu Studenckiego</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -10366,7 +10400,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10386,22 +10420,22 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J121" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>WallMuse (France)</t>
+          <t>Uczelniana Rada Samorządu Studenckiego</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10411,19 +10445,19 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Jeunesses Musicales Croatia HGM</t>
+          <t>Akademicki Związek Sportowy</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -10453,22 +10487,22 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J122" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Jeunesses Musicales Croatia HGM (Croatia)</t>
+          <t>Akademicki Związek Sportowy</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -10478,19 +10512,19 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AEC – Association Européenne des Conservatoires</t>
+          <t>Biuro Karier</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -10500,7 +10534,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10520,22 +10554,22 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J123" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>AEC – Association Européenne des Conservatoires (Belgium)</t>
+          <t>Biuro Karier</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10545,19 +10579,19 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KUNO</t>
+          <t>Klub Uczelniany PANS w Chełmie</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -10567,7 +10601,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10587,22 +10621,22 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J124" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>KUNO (Fine Art)</t>
+          <t>Klub Uczelniany PANS w Chełmie</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -10612,19 +10646,19 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cirrus</t>
+          <t>Chór Akademicki</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -10634,7 +10668,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10654,22 +10688,22 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J125" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Cirrus (Art and Design)</t>
+          <t>Chór Akademicki</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10679,19 +10713,19 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NordOpera</t>
+          <t>ALFA – Chełmskie Centrum Ewangelizacji</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -10701,7 +10735,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -10721,22 +10755,22 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="J126" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>NordOpera</t>
+          <t>ALFA – Chełmskie Centrum Ewangelizacji</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -10746,72 +10780,2484 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-10-20T16:01:27Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>Camp Leaders</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J127" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Camp Leaders – programy międzynarodowej wymiany i pracy wakacyjnej w USA</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Chełmska Biblioteka Publiczna</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J128" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Chełmska Biblioteka Publiczna</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Siłownia Extreme</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J129" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Siłownia Extreme</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Fabryka Sportu</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J130" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Fabryka Sportu</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Restauracja Kwiat Paproci</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J131" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Restauracja Kwiat Paproci</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Park Wodny Chełm</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J132" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Park Wodny Chełm</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Akademia Smaku Słowianka</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J133" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Akademia Smaku Słowianka</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Stacja Ratownictwa Medycznego w Chełmie</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J134" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>PANS w Chełmie podczas uroczystości z okazji 25-lecia działalności Stacji Ratownictwa Medycznego w Chełmie</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Zakład Doskonalenia Zawodowego w Chełmie</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J135" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>PANS w Chełmie podczas uroczystości z okazji 75-lecia działalności Zakładu Doskonalenia Zawodowego w Chełmie</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Pierwsza Społeczna Szkoła Podstawowa w Chełmie</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J136" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>PANS w Chełmie podczas inauguracji roku szkolnego 2026/2027 Pierwszej Społecznej Szkoły Podstawowej w Chełmie</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Akademia Górniczo-Hutnicza w Krakowie</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J137" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Wizyta przedstawicieli PANS w Chełmie w Akademii Górniczo-Hutniczej w Krakowie</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Zakład Produkcyjny GUMET z Kraśnika</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>r002</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="J138" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Wizyta przedstawicieli Zakładu Produkcyjnego GUMET z Kraśnika</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-10-22T11:48:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Zagreber Philharmonie</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>r003</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+        </is>
+      </c>
+      <c r="J139" s="1" t="inlineStr">
+        <is>
+          <t>https://www.kug.ac.at/</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Festanstellung für Fran Povijač als tiefer Hornist bei der Zagreber Philharmonie</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:00:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Tonhalle Orchester Zürich</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>r003</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+        </is>
+      </c>
+      <c r="J140" s="1" t="inlineStr">
+        <is>
+          <t>https://www.kug.ac.at/</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Engagement beim Tonhalle Orchester Zürich für Hornist Daniel Dubrovsky.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:00:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Florida International University</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J141" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Møller Institute, Churchill College, University of Cambridge</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J142" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Internationale Forschungskooperationen sind ein wichtiger Bestandteil meiner wissenschaftlichen Arbeit an der PH Weingarten. Im Rahmen des Fulbright Visiting Scholar Program 2026/27 werde ich einen Forschungsaufenthalt an der Florida International University absolvieren und dort zu antialevitischer und antisemitischer Propaganda sowie transnationalen Einflussstrategien forschen. Zugleich bin ich für zwei Jahre Faculty Fellow am Møller Institute, Churchill College, University of Cambridge, wo ich</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Universität Graz</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Österreich</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J143" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Universität Minho</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J144" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Universität Växjö</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Schweden</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J145" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/projekte/emic-steam-ecological-making-intercultural-cooperation-through-steam</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Am Projekt beteiligt sind Wissenschaftler:innen der Fächer Biologie (PH Weingarten), Making (PH Weingarten), Geographie (Universität Graz), Englisch (PH Weingarten), Kunst (Universität Minho), Erziehungswissenschaften (PH Weingarten, Universität Växjö) sowie Schulen aus den Projektländern Deutschland, Österreich, Portugal, Schweden sowie Luxemburg.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Santa Catarina</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Brasilien</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J146" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Donnerstag, 22.10.26 Präsentation von Dr. Elaine Roschel, Universidade Federal de Santa Catarina, Brasilien</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Stranmillis</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Nordirland</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J147" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Dienstag, 17.11.26 South Africa / Stranmillis (Nordirland)</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>UTALCA</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J148" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Dienstag, 01.12.26 Chile - Concepcion / UTALCA</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>more than 65 partner universities</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="J149" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Darüber hinaus organisiert das International Office Austausch- und Mobilitätsprogramme mit mehr als 65 Partnerhochschulen</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:58:36Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ELIA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J150" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/intranet/for-staff/internationalization/other-networks-and-bilateral-agreements</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>KHiO are partners in ELIA and Society for Artistic Research. We have several bilaterale agreements with partners outside of Europe.</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Society for Artistic Research</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J151" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/intranet/for-staff/internationalization/other-networks-and-bilateral-agreements</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>KHiO are partners in ELIA and Society for Artistic Research. We have several bilaterale agreements with partners outside of Europe.</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Conservatorio di Musica Santa Cecilia</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J152" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>The project is coordinated by Conservatorio di Musica Santa Cecilia (Rome) and the following project partners:</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Mozarteum University Salzburg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J153" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Mozarteum University Salzburg (Austria)</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Stockholm University of the Arts – SKH</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Stockholm University of the Arts – SKH (Sweden)</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Escola Superior de Música e Artes do Espetáculo do Porto</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J155" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Escola Superior de Música e Artes do Espetáculo do Porto (Portugal)</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Nova Opera</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J156" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Nova Opera (Ukraine)</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>WallMuse</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J157" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>WallMuse (France)</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jeunesses Musicales Croatia HGM</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J158" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Jeunesses Musicales Croatia HGM (Croatia)</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>AEC – Association Européenne des Conservatoires</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J159" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/research/research-in-the-arts/current-projects/opera-out-of-opera-2</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>AEC – Association Européenne des Conservatoires (Belgium)</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>KUNO</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J160" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>KUNO (Fine Art)</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Cirrus</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J161" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Cirrus (Art and Design)</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>NordOpera</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/intranet/for-staff/internationalization</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>NordOpera</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:01:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>Norteas</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
         </is>
       </c>
-      <c r="J127" s="1" t="inlineStr">
+      <c r="J163" s="1" t="inlineStr">
         <is>
           <t>https://khio.no/en/intranet/for-staff/internationalization</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="K163" t="inlineStr">
         <is>
           <t>Norteas (Performing Arts)</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>quote found on page</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t>2026-10-20T16:01:27Z</t>
         </is>
@@ -10945,6 +13391,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11064,7 +13546,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -11121,7 +13603,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -11178,7 +13660,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -11225,7 +13707,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22-100 Chełm</t>
+          <t>ul. Pocztowa 54</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -11240,7 +13722,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +13779,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-20T16:03:25Z</t>
+          <t>2026-10-22T11:48:01Z</t>
         </is>
       </c>
     </row>
@@ -11349,7 +13831,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -11406,7 +13888,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -11463,7 +13945,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -11520,7 +14002,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -11551,7 +14033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11676,19 +14158,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11698,30 +14180,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mag.a Lissa Gartler</t>
+          <t>Kamil Jaszczuk</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Büro der Vizerektorin für Lehre &amp; Internationales</t>
+          <t>Erasmus+ Program Coordinator</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>kjaszczuk@panschelm.edu.pl</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>82 562 06 13</t>
+        </is>
+      </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.kug.ac.at/kunst/gesellschaft/nachhaltigkeit/klimaneutraler-universitaetsbetrieb/betriebliches-mobilitaetsmanagement</t>
+          <t>https://panschelm.edu.pl/erasmus/</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Kontakt: Mag.a Lissa Gartler, Büro der Vizerektorin für Lehre &amp; Internationales, lissa.gartler(at)kug.ac.at</t>
+          <t>mgr Kamil Jaszczuk</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>International relations officer. She is the contact person for mobility and works in the office of the Vice Rector for Teaching and International Affairs.</t>
+          <t>Matches the contact your operators already spoke to. Mobility coordinator. Kamil Jaszczuk is explicitly listed as the contact for the Erasmus+ program at the institution with a direct phone number and email address.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -11731,200 +14221,192 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>name found on page</t>
+          <t>name, email, phone found on page</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tim Kaiser</t>
+          <t>Aneta Szostak</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Head of International Office</t>
+          <t>Head of the Promotion Department</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>kaisert@ph-weingarten.de</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0751/ 501-8421</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kaiser, Dr. Tim ... Leitung</t>
+          <t>13 października 2026 r. przedstawiciel Państwowej Akademii Nauk Stosowanych w Chełmie – Aneta Szostak – Kierownik Działu Promo...</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Matches the contact your operators already spoke to. Head of international relations. He is the head of the International Office and the contact person for international mobility. Own work email found on a page naming them.</t>
+          <t>Secretary / administration (last resort). Aneta Szostak is named as a head of department representing the institution at official events.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>name found on page</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kim Enderle</t>
+          <t>Piotr Różański</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>International Coordinator Erasmus / Auslandspraktika</t>
+          <t>Head of the Centre for Engineering Studies</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>prozanski@panschelm.edu.pl</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0751/ 501-8049</t>
+          <t>602 188 173</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>International Coordinator Erasmus / Auslandspraktika ... Enderle, Kim</t>
+          <t>mgr inż. Piotr Różański ... Kierownik Centrum Studiów Inżynierskich</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Institutional Erasmus+ coordinator. She is the designated coordinator for Erasmus and international internships.</t>
+          <t>Other role. Piotr Różański manages the Centre for Engineering Studies and handles cooperation with external entities.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>name, email, phone found on page</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+          <t>UNIVERSITAT FUR MUSIK UND DARSTELLENDE KUNST GRAZ (KUG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Beate Irion</t>
+          <t>Mag.a Lissa Gartler</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>International Coordinator Overseas</t>
+          <t>Büro der Vizerektorin für Lehre &amp; Internationales</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0751/ 501-8050</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+          <t>https://www.kug.ac.at/kunst/gesellschaft/nachhaltigkeit/klimaneutraler-universitaetsbetrieb/betriebliches-mobilitaetsmanagement</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>International Coordinator Übersee ... Irion, Beate</t>
+          <t>Kontakt: Mag.a Lissa Gartler, Büro der Vizerektorin für Lehre &amp; Internationales, lissa.gartler(at)kug.ac.at</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>International relations officer. She is the coordinator for overseas international partnerships.</t>
+          <t>International relations officer. She is the contact person for mobility and works in the office of the Vice Rector for Teaching and International Affairs.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11934,111 +14416,292 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ketil Akerø</t>
+          <t>Tim Kaiser</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Special Adviser</t>
+          <t>Head of International Office</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ketiaker@khio.no</t>
+          <t>kaisert@ph-weingarten.de</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>+47 911 82 910</t>
+          <t>0751/ 501-8421</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://khio.no/en/staff</t>
+          <t>https://www.ph-weingarten.de/de/studium/studierendenservice/auslandsaufenthalt/modulmobilitaet</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Ketil Akerø ... Special Adviser</t>
+          <t>Kaiser, Dr. Tim ... Leitung</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Matches the contact your operators already spoke to. Other role. Ketil Akerø is currently on file as a contact and serves as a Special Adviser in the Rectorate.</t>
+          <t>Matches the contact your operators already spoke to. Head of international relations. He is the head of the International Office and the contact person for international mobility. Own work email found on a page naming them.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kim Enderle</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>International Coordinator Erasmus / Auslandspraktika</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0751/ 501-8049</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>International Coordinator Erasmus / Auslandspraktika ... Enderle, Kim</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Institutional Erasmus+ coordinator. She is the designated coordinator for Erasmus and international internships.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>cited page was not read by the fetcher (cannot check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>r004</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PAEDAGOGISCHE HOCHSCHULE WEINGARTEN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Beate Irion</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>International Coordinator Overseas</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0751/ 501-8050</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.ph-weingarten.de/de/hochschule/international/international-office</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>International Coordinator Übersee ... Irion, Beate</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>International relations officer. She is the coordinator for overseas international partnerships.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>cited page was not read by the fetcher (cannot check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>r005</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ketil Akerø</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Special Adviser</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ketiaker@khio.no</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>+47 911 82 910</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://khio.no/en/staff</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ketil Akerø ... Special Adviser</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Matches the contact your operators already spoke to. Other role. Ketil Akerø is currently on file as a contact and serves as a Special Adviser in the Rectorate.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>r005</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KUNSTHOGSKOLEN I OSLO KHIO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Kjerstin Eek Jensen</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Senior Adviser internationalization</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>kjerjens@khio.no</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>+47 404 77 777</t>
         </is>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://khio.no/en/staff</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Kjerstin Eek Jensen ... Senior Adviser internationalization</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Mobility coordinator. Kjerstin Eek Jensen is the Senior Adviser for internationalization, handling incoming international exchange and agreements.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>name, email, phone found on page</t>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -12051,6 +14714,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12135,7 +14801,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -12172,7 +14838,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -12209,7 +14875,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>name not on page</t>
+          <t>cited page was not read by the fetcher (cannot check)</t>
         </is>
       </c>
     </row>
@@ -15761,7 +18427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -15790,7 +18456,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>International partners (14) - those with no country stated are last</t>
+          <t>International partners (50) - those with no country stated are last</t>
         </is>
       </c>
     </row>
@@ -15923,7 +18589,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -16182,7 +18848,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -16241,7 +18907,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Instytut Ochrony Roślin – PIB</t>
+          <t>Elektrolis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -16256,7 +18922,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>company</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16271,14 +18937,14 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enter Air Training Center</t>
+          <t>Finder Polska</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -16308,19 +18974,19 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Erasmus Student Network (ESN)</t>
+          <t>Zespół Szkół nr 3 w Kraśniku</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -16330,7 +18996,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>school</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -16345,54 +19011,125 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/erasmus/mobilnosc-studentow/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ISPCH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Campuses (2)</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Zakład Produkcyjny GUMET</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Campus</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Verified?</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Zakład Wyrobów Betonowych Wojciech Trykacz</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+          <t>Recykl S.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -16402,15 +19139,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chełm</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>yes</t>
@@ -16418,38 +19159,1295 @@
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>https://panschelm.edu.pl/</t>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>PROSOLUTIONS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Agro Antoniko Plus Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Recykl O. O. S.A.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gumet</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ZS 3 w Kraśniku</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Recykl Organizacja Odzysku S.A.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Fabryka Łożysk Tocznych w Kraśniku</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Katedra i Klinika Otorynolaryngologii, Chirurgii Głowy i Szyi Warszawskiego Uniwersytetu Medycznego</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Muzeum Ziemi Chełmskiej im. Wiktora Ambroziewicza w Chełmie</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Centrum Medyczne Aurismed</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Muzeum Regionalne w Krasnymstawie</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Haber</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sigma</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Erasmus Student Network (ESN)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/erasmus/mobilnosc-studentow/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Uczelniana Rada Samorządu Studenckiego</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Akademicki Związek Sportowy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biuro Karier</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Klub Uczelniany PANS w Chełmie</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chór Akademicki</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ALFA – Chełmskie Centrum Ewangelizacji</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Camp Leaders</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chełmska Biblioteka Publiczna</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Siłownia Extreme</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Fabryka Sportu</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Restauracja Kwiat Paproci</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Park Wodny Chełm</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Akademia Smaku Słowianka</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Stacja Ratownictwa Medycznego w Chełmie</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Zakład Doskonalenia Zawodowego w Chełmie</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Pierwsza Społeczna Szkoła Podstawowa w Chełmie</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/onboarding-w-pans-w-chelmie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Akademia Górniczo-Hutnicza w Krakowie</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Zakład Produkcyjny GUMET z Kraśnika</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/uczelnia/wspolpraca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Campuses (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Verified?</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Państwowa Akademia Nauk Stosowanych w Chełmie</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chełm</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>https://panschelm.edu.pl/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Centrum Lotnicze</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Depułtycze Królewskie</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>branch</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>https://panschelm.edu.pl/kontakt/</t>
         </is>
@@ -16472,8 +20470,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
